--- a/output/pdf_financials_xlsx/CXXI.xlsx
+++ b/output/pdf_financials_xlsx/CXXI.xlsx
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.408526</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.625461</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.234306</v>
       </c>
     </row>
     <row r="35">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.408526</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.625461</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.234306</v>
       </c>
     </row>
     <row r="37">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.330612</v>
+        <v>1.922086</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.275995</v>
+        <v>0.6505339999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.655413</v>
+        <v>1.421107</v>
       </c>
     </row>
     <row r="49">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E217" s="5" t="n">

--- a/output/pdf_financials_xlsx/CXXI.xlsx
+++ b/output/pdf_financials_xlsx/CXXI.xlsx
@@ -6695,7 +6695,11 @@
           <t>Proceeds from disposal of property and equipment 367,229</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CXXI.xlsx
+++ b/output/pdf_financials_xlsx/CXXI.xlsx
@@ -940,7 +940,7 @@
         <v>1.408976</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.207225</v>
+        <v>1.706012</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>14.270782</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>13.863454</v>
       </c>
     </row>
     <row r="57">
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>2.2119</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>2.81234</v>
       </c>
     </row>
     <row r="58">
@@ -1539,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.04961</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.34823</v>
       </c>
     </row>
     <row r="65">
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.486043</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.512941</v>
       </c>
     </row>
     <row r="68">
@@ -2114,12 +2114,10 @@
         <v>1.408976</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0.207225</v>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.706012</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>1.780182</v>
       </c>
     </row>
     <row r="101">
@@ -2132,12 +2130,10 @@
         <v>0.209289</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.05137</v>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.077696</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.1153</v>
       </c>
     </row>
     <row r="102">
@@ -2150,12 +2146,10 @@
         <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.69869</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>-0.049587</v>
       </c>
     </row>
     <row r="103">
@@ -2168,12 +2162,10 @@
         <v>0.130489</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.053196</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.06338100000000001</v>
       </c>
     </row>
     <row r="104">
@@ -2186,12 +2178,10 @@
         <v>-1.034911</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>0.356631</v>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.419139</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.33559</v>
       </c>
     </row>
     <row r="105">
@@ -2204,12 +2194,10 @@
         <v>0.207494</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>-0.014002</v>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022332</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>-0.006042</v>
       </c>
     </row>
     <row r="106">
@@ -2222,12 +2210,10 @@
         <v>-0.487639</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.291259</v>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.070997</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.458642</v>
       </c>
     </row>
     <row r="107">
@@ -2240,12 +2226,10 @@
         <v>0.022128</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.849559</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.236779</v>
       </c>
     </row>
     <row r="108">
@@ -2260,10 +2244,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2278,10 +2260,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2294,12 +2274,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.509871</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0.372018</v>
       </c>
     </row>
     <row r="111">
@@ -2312,12 +2290,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.406733</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>-0.244838</v>
       </c>
     </row>
     <row r="112">
@@ -2332,10 +2308,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2350,10 +2324,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2368,10 +2340,8 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2386,10 +2356,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2402,12 +2370,10 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.413647</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2422,10 +2388,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2440,10 +2404,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2480,10 +2442,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2498,10 +2458,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2516,10 +2474,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2534,10 +2490,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2552,10 +2506,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2570,10 +2522,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2588,10 +2538,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2628,10 +2576,8 @@
       <c r="C128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2666,12 +2612,10 @@
         <v>1.891772</v>
       </c>
       <c r="C130" s="3" t="n">
-        <v>2.408526</v>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.260568</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>2.625461</v>
       </c>
     </row>
     <row r="131">
@@ -2684,12 +2628,10 @@
         <v>0.007395</v>
       </c>
       <c r="C131" s="3" t="n">
-        <v>-0.000365</v>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.02977</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0.016078</v>
       </c>
     </row>
     <row r="132">
@@ -2702,12 +2644,10 @@
         <v>0.516754</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>0.852042</v>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.635107</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.391155</v>
       </c>
     </row>
     <row r="133">
@@ -2720,12 +2660,10 @@
         <v>2.408526</v>
       </c>
       <c r="C133" s="3" t="n">
-        <v>3.260568</v>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.625461</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>2.234306</v>
       </c>
     </row>
     <row r="134">
@@ -2738,12 +2676,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.406733</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>-0.244838</v>
       </c>
     </row>
     <row r="135">
@@ -2779,7 +2715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5921,20 +5857,20 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations after income tax expense (3,756,729)</t>
+          <t>Net loss from continuing operations after income tax expense</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>-3.223468</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>-0.051439</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.756729</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>-3.235638</v>
       </c>
     </row>
     <row r="98">
@@ -5950,24 +5886,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Accretion expense 509,871</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Accretion expense</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F98" s="5" t="n">
+        <v>0.509871</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.372018</v>
       </c>
     </row>
     <row r="99">
@@ -5983,20 +5919,20 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Amortization of right-of-use assets 574,686</t>
+          <t>Amortization of right-of-use assets</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>0.48034</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.082473</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.574686</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.655818</v>
       </c>
     </row>
     <row r="100">
@@ -6012,20 +5948,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 156,660</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" s="5" t="n">
-        <v>0.249071</v>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>-0.137807</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.15666</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>-0.147496</v>
       </c>
     </row>
     <row r="101">
@@ -6041,7 +5981,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 1,706,012</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6049,16 +5989,16 @@
           <t>DepreciationAndAmortization</t>
         </is>
       </c>
-      <c r="E101" s="5" t="n">
-        <v>1.408976</v>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.207225</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.706012</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>1.780182</v>
       </c>
     </row>
     <row r="102">
@@ -6074,22 +6014,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Foreign exchange gain -</t>
+          <t>Gain on change in fair value of derivative liabilities</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" s="5" t="n">
-        <v>-0.005788</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>-0.052257</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-0.02916</v>
       </c>
     </row>
     <row r="103">
@@ -6105,26 +6043,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Share-based compensation 849,559</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="n">
-        <v>0.022128</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.293675</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.187241</v>
       </c>
     </row>
     <row r="104">
@@ -6140,20 +6072,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>(Gain) loss on change in fair value of derivative liabilities (52,257)</t>
+          <t>Interest and accretion income included in other income</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" s="5" t="n">
-        <v>0.451372</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>-0.022189</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>-0.065188</v>
       </c>
     </row>
     <row r="105">
@@ -6169,22 +6103,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gain on termination of sales-type lease -</t>
+          <t>Loss on extinguishment of EFF liability</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" s="5" t="n">
-        <v>-0.503544</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="5" t="n">
+        <v>0.442543</v>
       </c>
     </row>
     <row r="106">
@@ -6200,22 +6134,20 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Loss on disposal of assets 155,692</t>
+          <t>(Gain) loss on disposal of assets</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" s="5" t="n">
-        <v>0.011655</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0.155692</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>-0.007446</v>
       </c>
     </row>
     <row r="107">
@@ -6231,22 +6163,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Impairment loss -</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" s="5" t="n">
-        <v>1.202227</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>0.849559</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.236779</v>
       </c>
     </row>
     <row r="108">
@@ -6257,27 +6191,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Interest expense 293,675</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" s="5" t="n">
-        <v>0.03521</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0.077696</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.1153</v>
       </c>
     </row>
     <row r="109">
@@ -6293,24 +6229,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Receivables 77,696</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>0.209289</v>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>-0.05137</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.69869</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>-0.049587</v>
       </c>
     </row>
     <row r="110">
@@ -6326,20 +6262,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Inventory (698,690)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" s="5" t="n">
-        <v>1.948095</v>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>-0.074639</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.053196</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.06338100000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6355,20 +6295,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits (53,196)</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" s="5" t="n">
-        <v>0.130489</v>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>0.158526</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.419139</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.33559</v>
       </c>
     </row>
     <row r="112">
@@ -6384,24 +6328,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (419,139)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="n">
-        <v>-1.034911</v>
-      </c>
-      <c r="F112" s="5" t="n">
-        <v>0.356631</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Settlement liability</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="113">
@@ -6417,20 +6359,20 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Income taxes payable (7,396,432)</t>
+          <t>Income taxes payable</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" s="5" t="n">
-        <v>1.983014</v>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.510551</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.396432</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>-1.179137</v>
       </c>
     </row>
     <row r="114">
@@ -6446,7 +6388,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Uncertain tax position 9,822,797</t>
+          <t>Uncertain tax position</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -6455,15 +6397,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="5" t="n">
+        <v>9.822797</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>3.539212</v>
       </c>
     </row>
     <row r="115">
@@ -6479,7 +6417,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Deferred revenue 22,332</t>
+          <t>Deferred revenue</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6487,16 +6425,16 @@
           <t>ChangeInOtherWorkingCapital</t>
         </is>
       </c>
-      <c r="E115" s="5" t="n">
-        <v>0.207494</v>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>-0.014002</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022332</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>-0.006042</v>
       </c>
     </row>
     <row r="116">
@@ -6512,20 +6450,20 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lease liabilities (426,884)</t>
+          <t>Lease liabilities</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>-0.310394</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>-0.05934</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.426884</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>-0.545231</v>
       </c>
     </row>
     <row r="117">
@@ -6541,20 +6479,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cash provided by operating activities of continuing operations 1,365,653</t>
+          <t>Cash provided by operating activities of continuing operations</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" s="5" t="n">
-        <v>3.261255</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>0.90462</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.365653</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>1.363139</v>
       </c>
     </row>
     <row r="118">
@@ -6570,20 +6508,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cash (used in) provided by operating activities of discontinued operations (176,487)</t>
+          <t>Cash used in operating activities of discontinued operations</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" s="5" t="n">
-        <v>0.06859899999999999</v>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.006861</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.176487</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>-0.00808</v>
       </c>
     </row>
     <row r="119">
@@ -6599,20 +6537,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Purchases of property and equipment (406,733)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" s="5" t="n">
-        <v>-0.521579</v>
+          <t>Purchases of property and equipment</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>-0.051483</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.406733</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>-0.244838</v>
       </c>
     </row>
     <row r="120">
@@ -6628,17 +6570,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Proceeds from termination of sales-type lease and disposal of licenses -</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Purchases of intangible assets</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>-3.413647</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6659,7 +6605,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Purchases of licenses as part of Deep Roots acquisition (3,413,647)</t>
+          <t>Proceeds from disposal of assets</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -6668,15 +6614,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F121" s="5" t="n">
+        <v>0.367229</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="122">
@@ -6692,28 +6634,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Proceeds from disposal of property and equipment 367,229</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+          <t>Cash used in investing activities of continuing operations</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F122" s="5" t="n">
+        <v>-3.453151</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>-0.219838</v>
       </c>
     </row>
     <row r="123">
@@ -6729,15 +6663,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cash used in investing activities of continuing operations (3,453,151)</t>
+          <t>Cash provided by investing activities of discontinued operations</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" s="5" t="n">
-        <v>-0.121579</v>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>-0.051483</v>
+        <v>0.331936</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6753,12 +6689,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cash provided by investing activities of discontinued operations 331,936</t>
+          <t>Proceeds from issuance of debenture units</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -6767,10 +6703,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F124" s="5" t="n">
+        <v>2.920562</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6791,22 +6725,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Settlement of earn out shares -</t>
+          <t>Interest payments received on note receivable</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" s="5" t="n">
-        <v>-0.575136</v>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G125" s="5" t="n">
+        <v>0.034</v>
       </c>
     </row>
     <row r="126">
@@ -6822,7 +6756,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of debenture units 2,920,562</t>
+          <t>Principal repayments on convertible debentures</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -6831,15 +6765,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" s="5" t="n">
+        <v>-0.677732</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>-1.286179</v>
       </c>
     </row>
     <row r="127">
@@ -6855,22 +6785,20 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Principal repayments on promissory note payable -</t>
+          <t>Interest paid in cash</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
-      <c r="E127" s="5" t="n">
-        <v>-2.026667</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>-0.293675</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>-0.187241</v>
       </c>
     </row>
     <row r="128">
@@ -6886,7 +6814,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Principal repayments on convertible debentures (677,732)</t>
+          <t>Repurchase and cancellation of shares</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -6895,15 +6823,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F128" s="5" t="n">
+        <v>-0.27673</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>-0.103034</v>
       </c>
     </row>
     <row r="129">
@@ -6919,22 +6843,20 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Interest paid in cash (293,675)</t>
+          <t>Cash (used in) provided by financing activities of continuing operations</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" s="5" t="n">
-        <v>-0.051562</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>1.672425</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>-1.542454</v>
       </c>
     </row>
     <row r="130">
@@ -6950,7 +6872,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cancellation of shares (276,730)</t>
+          <t>Cash used in financing activities of discontinued operations</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -6959,10 +6881,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F130" s="5" t="n">
+        <v>-0.405253</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6983,22 +6903,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cash provided by (used in) financing activities of continuing operations 1,672,425</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" s="5" t="n">
-        <v>-2.653365</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Effect of foreign exchange on cash</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>0.02977</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.016078</v>
       </c>
     </row>
     <row r="132">
@@ -7014,20 +6936,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cash used in financing activities of discontinued operations (405,253)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" s="5" t="n">
-        <v>-0.045551</v>
+          <t>Change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.007591</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.635107</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>-0.391155</v>
       </c>
     </row>
     <row r="133">
@@ -7043,24 +6969,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash 29,770</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>EffectOfExchangeRateChanges</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="n">
-        <v>0.007395</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>-0.000365</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.260568</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>2.625461</v>
       </c>
     </row>
     <row r="134">
@@ -7076,20 +7002,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Change in cash during the year (635,107)</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" s="5" t="n">
-        <v>0.516754</v>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.852042</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.625461</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>2.234306</v>
       </c>
     </row>
     <row r="135">
@@ -7100,29 +7030,25 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cash, beginning of year 3,260,568</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="n">
-        <v>1.891772</v>
+          <t>Income tax paid in cash</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>2.408526</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.5</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="136">
@@ -7133,29 +7059,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cash, end of year 2,625,461</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="n">
-        <v>2.408526</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>3.260568</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest payments received on note receivable</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.034</v>
       </c>
     </row>
     <row r="137">
@@ -7171,22 +7095,20 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Income tax paid in cash 1,500,000</t>
+          <t>Interest paid in cash</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" s="5" t="n">
-        <v>1.25015</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>0.293675</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>-0.187241</v>
       </c>
     </row>
     <row r="138">
@@ -7202,17 +7124,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Interest paid in cash 293,675</t>
+          <t>Addition in right-of-use assets and lease liabilities</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" s="5" t="n">
-        <v>0.051562</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>1.221143</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7228,22 +7150,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Supplemental disclosure of cash flow information</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Addition in right -of-use assets and lease liabilities 1,221,143</t>
+          <t>Net loss from continuing operations after income tax expense (3,756,729)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" s="5" t="n">
-        <v>0.924105</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.223468</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>-0.051439</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -7257,15 +7177,25 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>March 31, January</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>Accretion expense 509,871</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -7291,17 +7221,15 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations after income tax expense (51,439)</t>
+          <t>Amortization of right-of-use assets 574,686</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" s="5" t="n">
-        <v>-3.223468</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.48034</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>0.082473</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7322,17 +7250,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Amortization of right-of-use assets 82,473</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>Deferred income tax recovery 156,660</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="n">
-        <v>0.48034</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.249071</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>-0.137807</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7353,17 +7283,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (137,807)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>Depreciation and amortization 1,706,012</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E143" s="5" t="n">
-        <v>0.249071</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.408976</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.207225</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7384,16 +7316,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 207,225</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Foreign exchange gain -</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" s="5" t="n">
-        <v>1.408976</v>
+        <v>-0.005788</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -7419,12 +7347,16 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>(Gain) loss on change in fair value of derivative liability (22,189)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Share-based compensation 849,559</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E145" s="5" t="n">
-        <v>0.451372</v>
+        <v>0.022128</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -7450,17 +7382,15 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Gain on termination of sales-type lease and disposal of licenses -</t>
+          <t>(Gain) loss on change in fair value of derivative liabilities (52,257)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" s="5" t="n">
-        <v>-0.503544</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.451372</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>-0.022189</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7481,12 +7411,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Loss on disposal of assets -</t>
+          <t>Gain on termination of sales-type lease -</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" s="5" t="n">
-        <v>0.011655</v>
+        <v>-0.503544</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -7512,12 +7442,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Interest expense -</t>
+          <t>Loss on disposal of assets 155,692</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" s="5" t="n">
-        <v>0.03521</v>
+        <v>0.011655</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -7543,16 +7473,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Share-based compensation -</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Impairment loss -</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" s="5" t="n">
-        <v>0.022128</v>
+        <v>1.202227</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -7573,17 +7499,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Receivables (51,370)</t>
+          <t>Interest expense 293,675</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" s="5" t="n">
-        <v>0.209289</v>
+        <v>0.03521</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -7609,17 +7535,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Inventory (74,639)</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Receivables 77,696</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E151" s="5" t="n">
-        <v>1.948095</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.209289</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>-0.05137</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -7640,21 +7568,15 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits 158,526</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Inventory (698,690)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" s="5" t="n">
-        <v>0.130489</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.948095</v>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>-0.074639</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -7675,21 +7597,15 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 356,631</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Prepaid expenses and deposits (53,196)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" s="5" t="n">
-        <v>-1.034911</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.130489</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>0.158526</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -7710,17 +7626,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Income taxes payable 510,551</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (419,139)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
-        <v>1.983014</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.034911</v>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>0.356631</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -7741,17 +7659,15 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Deferred revenue (14,002)</t>
+          <t>Income taxes payable (7,396,432)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" s="5" t="n">
-        <v>0.207494</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.983014</v>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>0.510551</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -7772,12 +7688,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Lease liabilities (59,340)</t>
+          <t>Uncertain tax position 9,822,797</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" s="5" t="n">
-        <v>-0.310394</v>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -7803,17 +7721,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cash provided by operating activities of continuing operations 904,620</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Deferred revenue 22,332</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
       <c r="E157" s="5" t="n">
-        <v>3.261255</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.207494</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>-0.014002</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -7834,17 +7754,15 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Cash provided by operating activities of discontinued operations 6,861</t>
+          <t>Lease liabilities (426,884)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" s="5" t="n">
-        <v>0.06859899999999999</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.310394</v>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>-0.05934</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -7860,22 +7778,20 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Purchases of property and equipment (51,483)</t>
+          <t>Cash provided by operating activities of continuing operations 1,365,653</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" s="5" t="n">
-        <v>-0.521579</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.261255</v>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>0.90462</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -7891,22 +7807,20 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cash used in investing activities of continuing operations (51,483)</t>
+          <t>Cash (used in) provided by operating activities of discontinued operations (176,487)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" s="5" t="n">
-        <v>-0.121579</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06859899999999999</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>0.006861</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -7927,19 +7841,15 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cash provided by investing activities of discontinued operations -</t>
+          <t>Purchases of property and equipment (406,733)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E161" s="5" t="n">
+        <v>-0.521579</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>-0.051483</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -7955,17 +7865,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Interest paid in cash -</t>
+          <t>Proceeds from termination of sales-type lease and disposal of licenses -</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" s="5" t="n">
-        <v>-0.051562</v>
+        <v>0.4</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -7986,17 +7896,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cash used in financing activities of continuing operations -</t>
+          <t>Purchases of licenses as part of Deep Roots acquisition (3,413,647)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" s="5" t="n">
-        <v>-2.653365</v>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -8017,17 +7929,23 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Cash used in financing activities of discontinued operations (7,591)</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" s="5" t="n">
-        <v>-0.045551</v>
+          <t>Proceeds from disposal of property and equipment 367,229</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -8048,26 +7966,20 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash (365)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>EffectOfExchangeRateChanges</t>
-        </is>
-      </c>
+          <t>Cash used in investing activities of continuing operations (3,453,151)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" s="5" t="n">
-        <v>0.007395</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.121579</v>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>-0.051483</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -8083,21 +7995,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Change in cash during the year 852,042</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E166" s="5" t="n">
-        <v>0.516754</v>
+          <t>Cash provided by investing activities of discontinued operations 331,936</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -8123,16 +8033,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cash beginning of year 2,408,526</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Settlement of earn out shares -</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" s="5" t="n">
-        <v>1.891772</v>
+        <v>-0.575136</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -8158,16 +8064,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cash end of year 3,260,568</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="n">
-        <v>2.408526</v>
+          <t>Proceeds from issuance of debenture units 2,920,562</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -8188,17 +8092,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Supplemental disclosure of cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Income tax paid in cash -</t>
+          <t>Principal repayments on promissory note payable -</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" s="5" t="n">
-        <v>1.25015</v>
+        <v>-2.026667</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -8219,17 +8123,19 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Supplemental disclosure of cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Interest paid in cash -</t>
+          <t>Principal repayments on convertible debentures (677,732)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" s="5" t="n">
-        <v>0.051562</v>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -8250,17 +8156,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Supplemental disclosure of cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Additions in right-of-use assets and lease liabilities (Note 12) -</t>
+          <t>Interest paid in cash (293,675)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" s="5" t="n">
-        <v>0.924105</v>
+        <v>-0.051562</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -8276,29 +8182,29 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Revenue 30,117,880</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E172" s="5" t="n">
-        <v>28.2852</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>4.46495</v>
+          <t>Cancellation of shares (276,730)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -8309,29 +8215,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Cost of sales 17,558,940</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Cash provided by (used in) financing activities of continuing operations 1,672,425</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" s="5" t="n">
-        <v>17.135434</v>
-      </c>
-      <c r="F173" s="5" t="n">
-        <v>2.68865</v>
+        <v>-2.653365</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -8342,29 +8246,25 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Gross profit 12,558,940</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Cash used in financing activities of discontinued operations (405,253)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" s="5" t="n">
-        <v>11.149766</v>
+        <v>-0.045551</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>1.7763</v>
+        <v>-0.007591</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -8375,29 +8275,29 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 11,277,284</t>
+          <t>Effect of foreign exchange on cash 29,770</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>EffectOfExchangeRateChanges</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>9.677738</v>
+        <v>0.007395</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>1.486394</v>
+        <v>-0.000365</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -8408,29 +8308,25 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Income from operations 1,281,656</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Change in cash during the year (635,107)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" s="5" t="n">
-        <v>1.472028</v>
+        <v>0.516754</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>0.289906</v>
+        <v>0.852042</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -8441,25 +8337,29 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Gain (loss) on change in fair value of derivative liabilities 52,257</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Cash, beginning of year 3,260,568</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E177" s="5" t="n">
-        <v>-0.451372</v>
+        <v>1.891772</v>
       </c>
       <c r="F177" s="5" t="n">
-        <v>0.022189</v>
+        <v>2.408526</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -8470,27 +8370,29 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Gain on termination of sales-type lease -</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Cash, end of year 2,625,461</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="n">
-        <v>0.503544</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.408526</v>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>3.260568</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -8501,24 +8403,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Accretion expense (509,871)</t>
+          <t>Income tax paid in cash 1,500,000</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E179" s="5" t="n">
+        <v>1.25015</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -8534,22 +8434,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Loss on disposal of assets (155,692)</t>
+          <t>Interest paid in cash 293,675</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" s="5" t="n">
-        <v>-0.011655</v>
+        <v>0.051562</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -8565,22 +8465,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Impairment loss -</t>
+          <t>Addition in right -of-use assets and lease liabilities 1,221,143</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" s="5" t="n">
-        <v>-1.202227</v>
+        <v>0.924105</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -8596,22 +8496,18 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>ended</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Interest expense (293,675)</t>
+          <t>March 31, January</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" s="5" t="n">
-        <v>-0.03521</v>
+        <v>3.1e-05</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -8627,29 +8523,27 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Other income 20,246</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Net loss from continuing operations after income tax expense (51,439)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" s="5" t="n">
-        <v>-0.016451</v>
-      </c>
-      <c r="F183" s="5" t="n">
-        <v>0.009209</v>
+        <v>-3.223468</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -8660,29 +8554,27 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Net income from continuing operations before income tax expense 394,921</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Amortization of right-of-use assets 82,473</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" s="5" t="n">
-        <v>0.258657</v>
-      </c>
-      <c r="F184" s="5" t="n">
-        <v>0.321304</v>
+        <v>0.48034</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -8693,25 +8585,27 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Income tax expense (4,151,650)</t>
+          <t>Deferred income tax recovery (137,807)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" s="5" t="n">
-        <v>-3.482125</v>
-      </c>
-      <c r="F185" s="5" t="n">
-        <v>-0.372743</v>
+        <v>0.249071</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -8722,25 +8616,31 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations after income tax expense (3,756,729)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Depreciation and amortization 207,225</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E186" s="5" t="n">
-        <v>-3.223468</v>
-      </c>
-      <c r="F186" s="5" t="n">
-        <v>-0.051439</v>
+        <v>1.408976</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -8751,25 +8651,27 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Net loss from discontinued operations after income tax expense (212,813)</t>
+          <t>(Gain) loss on change in fair value of derivative liability (22,189)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" s="5" t="n">
-        <v>-0.081817</v>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>-0.022965</v>
+        <v>0.451372</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -8780,25 +8682,27 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ended</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Net loss (3,969,542)</t>
+          <t>Gain on termination of sales-type lease and disposal of licenses -</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" s="5" t="n">
-        <v>-3.305285</v>
-      </c>
-      <c r="F188" s="5" t="n">
-        <v>-0.074404</v>
+        <v>-0.503544</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -8809,25 +8713,27 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment 133,050</t>
+          <t>Loss on disposal of assets -</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" s="5" t="n">
-        <v>0.015089</v>
-      </c>
-      <c r="F189" s="5" t="n">
-        <v>0.000808</v>
+        <v>0.011655</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -8838,25 +8744,27 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Comprehensive loss (3,836,492)</t>
+          <t>Interest expense -</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" s="5" t="n">
-        <v>-3.290196</v>
-      </c>
-      <c r="F190" s="5" t="n">
-        <v>-0.07359599999999999</v>
+        <v>0.03521</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -8867,25 +8775,31 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share from continuing operations (0.03)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Share-based compensation -</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E191" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="F191" s="5" t="n">
-        <v>0</v>
+        <v>0.022128</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -8896,25 +8810,27 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share from discontinued operations (0.00)</t>
+          <t>Receivables (51,370)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" s="5" t="n">
-        <v>0</v>
+        <v>0.209289</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -8925,29 +8841,27 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (0.03)</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Inventory (74,639)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="F193" s="5" t="n">
-        <v>0</v>
+        <v>1.948095</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -8958,29 +8872,31 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic 119,794,951</t>
+          <t>Prepaid expenses and deposits 158,526</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>120.047814</v>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>120.047814</v>
+        <v>0.130489</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -8991,29 +8907,31 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - diluted 120,588,044</t>
+          <t>Accounts payable and accrued liabilities 356,631</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>122.880907</v>
-      </c>
-      <c r="F195" s="5" t="n">
-        <v>122.880907</v>
+        <v>-1.034911</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -9024,25 +8942,27 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Balance, January 31, 2023 120,047,814 105,445,792 628,141 (2,287,145)</t>
+          <t>Income taxes payable 510,551</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" s="5" t="n">
-        <v>34.315076</v>
-      </c>
-      <c r="F196" s="5" t="n">
-        <v>-69.471712</v>
+        <v>1.983014</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -9053,22 +8973,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Share-based compensation - 22,128 - -</t>
+          <t>Deferred revenue (14,002)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" s="5" t="n">
-        <v>0.022128</v>
+        <v>0.207494</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -9084,25 +9004,27 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive income for the year - - - 15,089</t>
+          <t>Lease liabilities (59,340)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" s="5" t="n">
-        <v>-3.290196</v>
-      </c>
-      <c r="F198" s="5" t="n">
-        <v>-3.305285</v>
+        <v>-0.310394</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -9113,25 +9035,27 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Balance, January 31, 2024 120,047,814 105,467,920 628,141 (2,272,056)</t>
+          <t>Cash provided by operating activities of continuing operations 904,620</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" s="5" t="n">
-        <v>31.047008</v>
-      </c>
-      <c r="F199" s="5" t="n">
-        <v>-72.77699699999999</v>
+        <v>3.261255</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -9142,25 +9066,27 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive income for the year - - - 808</t>
+          <t>Cash provided by operating activities of discontinued operations 6,861</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" s="5" t="n">
-        <v>-0.07359599999999999</v>
-      </c>
-      <c r="F200" s="5" t="n">
-        <v>-0.074404</v>
+        <v>0.06859899999999999</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -9171,25 +9097,27 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2024 120,047,814 105,467,920 628,141 (2,271,248)</t>
+          <t>Purchases of property and equipment (51,483)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" s="5" t="n">
-        <v>30.973412</v>
-      </c>
-      <c r="F201" s="5" t="n">
-        <v>-72.851401</v>
+        <v>-0.521579</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -9200,22 +9128,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Warrants issued in private placement - 966,028 - -</t>
+          <t>Cash used in investing activities of continuing operations (51,483)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" s="5" t="n">
-        <v>0.966028</v>
+        <v>-0.121579</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -9231,22 +9159,24 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Share-based compensation - 849,559 - -</t>
+          <t>Cash provided by investing activities of discontinued operations -</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" s="5" t="n">
-        <v>0.849559</v>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -9262,22 +9192,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Cancellation of shares (2,051,000) (276,730) - -</t>
+          <t>Interest paid in cash -</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" s="5" t="n">
-        <v>-0.27673</v>
+        <v>-0.051562</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -9293,25 +9223,27 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive income for the year - - - 133,050</t>
+          <t>Cash used in financing activities of continuing operations -</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" s="5" t="n">
-        <v>-3.836492</v>
-      </c>
-      <c r="F205" s="5" t="n">
-        <v>-3.969542</v>
+        <v>-2.653365</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -9322,25 +9254,27 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2025 117,996,814 107,006,777 628,141 (2,138,198)</t>
+          <t>Cash used in financing activities of discontinued operations (7,591)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" s="5" t="n">
-        <v>28.675777</v>
-      </c>
-      <c r="F206" s="5" t="n">
-        <v>-76.820943</v>
+        <v>-0.045551</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -9351,18 +9285,26 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>March 31, January</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>Effect of foreign exchange on cash (365)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
       <c r="E207" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.007395</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9378,22 +9320,26 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Revenue 4,464,950</t>
+          <t>Change in cash during the year 852,042</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E208" s="5" t="n">
-        <v>28.2852</v>
+        <v>0.516754</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -9409,22 +9355,26 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Cost of sales 2,688,650</t>
+          <t>Cash beginning of year 2,408,526</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>17.135434</v>
+        <v>1.891772</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -9440,22 +9390,26 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Gross profit 1,776,300</t>
+          <t>Cash end of year 3,260,568</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E210" s="5" t="n">
-        <v>11.149766</v>
+        <v>2.408526</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -9471,22 +9425,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Supplemental disclosure of cash flow information</t>
+        </is>
+      </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 1,486,394</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Income tax paid in cash -</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" s="5" t="n">
-        <v>9.677738</v>
+        <v>1.25015</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -9502,22 +9456,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Supplemental disclosure of cash flow information</t>
+        </is>
+      </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Income from operations 289,906</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Interest paid in cash -</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
       <c r="E212" s="5" t="n">
-        <v>1.472028</v>
+        <v>0.051562</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -9533,18 +9487,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Supplemental disclosure of cash flow information</t>
+        </is>
+      </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Gain (loss) on change in fair value of derivative liability 22,189</t>
+          <t>Additions in right-of-use assets and lease liabilities (Note 12) -</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" s="5" t="n">
-        <v>-0.451372</v>
+        <v>0.924105</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -9566,22 +9524,20 @@
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Gain on termination of sales-type lease and disposal of licenses -</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" s="5" t="n">
-        <v>0.503544</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>30.11788</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>32.614513</v>
       </c>
     </row>
     <row r="215">
@@ -9593,22 +9549,20 @@
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Loss on disposal of assets -</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" s="5" t="n">
-        <v>-0.011655</v>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>17.55894</v>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>19.009393</v>
       </c>
     </row>
     <row r="216">
@@ -9620,22 +9574,20 @@
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Impairment loss -</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" s="5" t="n">
-        <v>-1.202227</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>12.55894</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>13.60512</v>
       </c>
     </row>
     <row r="217">
@@ -9647,26 +9599,20 @@
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Interest expense -</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E217" s="5" t="n">
-        <v>-0.03521</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Selling, general and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>11.277284</v>
+      </c>
+      <c r="G217" s="5" t="n">
+        <v>11.326833</v>
       </c>
     </row>
     <row r="218">
@@ -9678,26 +9624,20 @@
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Other expense 9,209</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E218" s="5" t="n">
-        <v>-0.016451</v>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Income from operations</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>1.281656</v>
+      </c>
+      <c r="G218" s="5" t="n">
+        <v>2.278287</v>
       </c>
     </row>
     <row r="219">
@@ -9709,26 +9649,20 @@
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Net income from continuing operations before income tax expense 321,304</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E219" s="5" t="n">
-        <v>0.258657</v>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accretion expense</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>-0.509871</v>
+      </c>
+      <c r="G219" s="5" t="n">
+        <v>-0.372018</v>
       </c>
     </row>
     <row r="220">
@@ -9740,22 +9674,20 @@
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Income tax expense (372,743)</t>
+          <t>Gain on change in fair value of derivative liabilities</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
-      <c r="E220" s="5" t="n">
-        <v>-3.482125</v>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>0.052257</v>
+      </c>
+      <c r="G220" s="5" t="n">
+        <v>0.02916</v>
       </c>
     </row>
     <row r="221">
@@ -9767,22 +9699,20 @@
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations after income tax expense (51,439)</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
-      <c r="E221" s="5" t="n">
-        <v>-3.223468</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>-0.293675</v>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>-0.187241</v>
       </c>
     </row>
     <row r="222">
@@ -9794,22 +9724,22 @@
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Net loss from discontinued operations after income tax expense (22,965)</t>
+          <t>Loss on settlement of legal proceedings</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
-      <c r="E222" s="5" t="n">
-        <v>-0.081817</v>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G222" s="5" t="n">
+        <v>-0.442543</v>
       </c>
     </row>
     <row r="223">
@@ -9821,22 +9751,20 @@
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Net loss (74,404)</t>
+          <t>Gain (loss) on disposal of assets</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" s="5" t="n">
-        <v>-3.305285</v>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>-0.155692</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>0.007446</v>
       </c>
     </row>
     <row r="224">
@@ -9845,29 +9773,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment 808</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" s="5" t="n">
-        <v>0.015089</v>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>0.020246</v>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>0.06569899999999999</v>
       </c>
     </row>
     <row r="225">
@@ -9876,29 +9798,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Comprehensive loss (73,596)</t>
+          <t>Net income from continuing operations before income tax expense</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" s="5" t="n">
-        <v>-3.290196</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>0.394921</v>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>1.37879</v>
       </c>
     </row>
     <row r="226">
@@ -9907,29 +9823,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share from continuing operations (0.00)</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
-      <c r="E226" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="n">
+        <v>-4.15165</v>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>-4.614428</v>
       </c>
     </row>
     <row r="227">
@@ -9938,33 +9848,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
+      <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (0.00)</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E227" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss from continuing operations after income tax expense</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="n">
+        <v>-3.756729</v>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>-3.235638</v>
       </c>
     </row>
     <row r="228">
@@ -9973,29 +9873,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
+      <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted 120,047,814</t>
+          <t>Net loss from discontinued operations after income tax expense</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
-      <c r="E228" s="5" t="n">
-        <v>120.047814</v>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>-0.212813</v>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>-0.00808</v>
       </c>
     </row>
     <row r="229">
@@ -10004,29 +9898,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Balance, January 31, 2023 120,047,814 105,445,792 628,141 (2,287,145) (69,471,712)</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" s="5" t="n">
-        <v>34.315076</v>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="n">
+        <v>-3.969542</v>
+      </c>
+      <c r="G229" s="5" t="n">
+        <v>-3.243718</v>
       </c>
     </row>
     <row r="230">
@@ -10037,27 +9925,25 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Share-based compensation - 22,128 - - -</t>
+          <t>Cumulative translation adjustment</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" s="5" t="n">
-        <v>0.022128</v>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>0.13305</v>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>-0.047417</v>
       </c>
     </row>
     <row r="231">
@@ -10068,27 +9954,25 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Net loss and other comprehensive income for the year - - - 15,089 (3,305,285)</t>
+          <t>Comprehensive loss</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" s="5" t="n">
-        <v>-3.290196</v>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="n">
+        <v>-3.836492</v>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>-3.291135</v>
       </c>
     </row>
     <row r="232">
@@ -10099,27 +9983,25 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Balance, January 31, 2024 120,047,814 105,467,920 628,141 (2,272,056) (72,776,997)</t>
+          <t>Basic and diluted loss per share from continuing operations</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
-      <c r="E232" s="5" t="n">
-        <v>31.047008</v>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>-3e-08</v>
       </c>
     </row>
     <row r="233">
@@ -10130,27 +10012,25 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Net loss and other comprehensive income for the year - - - 808 (74,404)</t>
+          <t>Basic and diluted loss per share from discontinued operations</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
-      <c r="E233" s="5" t="n">
-        <v>-0.07359599999999999</v>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -10161,24 +10041,2384 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - basic</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>119.794951</v>
+      </c>
+      <c r="G235" s="5" t="n">
+        <v>117.910795</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - diluted</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F236" s="5" t="n">
+        <v>120.588044</v>
+      </c>
+      <c r="G236" s="5" t="n">
+        <v>118.466588</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2024 120,047,814 105,467,920 - - 628,141 (2,271,248)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="n">
+        <v>30.973412</v>
+      </c>
+      <c r="G237" s="5" t="n">
+        <v>-72.851401</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Warrants issued in private placement - 966,028 - - - -</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="n">
+        <v>0.966028</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Share-based compensation - 849,559 - - - -</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="n">
+        <v>0.849559</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Repurchase and cancellation of shares (2,051,000) (276,730) - - - -</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F240" s="5" t="n">
+        <v>-0.27673</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive income - - - - - 133,050</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="n">
+        <v>-3.836492</v>
+      </c>
+      <c r="G241" s="5" t="n">
+        <v>-3.969542</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2025 117,996,814 107,006,777 - - 628,141 (2,138,198)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F242" s="5" t="n">
+        <v>28.675777</v>
+      </c>
+      <c r="G242" s="5" t="n">
+        <v>-76.820943</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Share-based compensation - 236,779 - - - -</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="n">
+        <v>0.236779</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Repurchase and cancellation of shares (479,500) (103,034) - - - -</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="n">
+        <v>-0.103034</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Exercise of debentures 318,753 103,544 - - - -</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="n">
+        <v>0.103544</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Issuance of subordinate shares - - 100,000,000 72 - -</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" s="5" t="n">
+        <v>7.2e-05</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>EFF Settlement - - - - (188,698) -</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="n">
+        <v>-0.188698</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - - - - (47,417)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="n">
+        <v>-3.291135</v>
+      </c>
+      <c r="G248" s="5" t="n">
+        <v>-3.243718</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>#           $           #</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2026 117,836,067 107,244,066 100,000,000 72 439,443 (2,185,615)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="n">
+        <v>25.433305</v>
+      </c>
+      <c r="G249" s="5" t="n">
+        <v>-80.064661</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Revenue 30,117,880</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="n">
+        <v>28.2852</v>
+      </c>
+      <c r="F250" s="5" t="n">
+        <v>4.46495</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Cost of sales 17,558,940</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="n">
+        <v>17.135434</v>
+      </c>
+      <c r="F251" s="5" t="n">
+        <v>2.68865</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Gross profit 12,558,940</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="n">
+        <v>11.149766</v>
+      </c>
+      <c r="F252" s="5" t="n">
+        <v>1.7763</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Selling, general and administrative expenses 11,277,284</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="n">
+        <v>9.677738</v>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>1.486394</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Income from operations 1,281,656</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="n">
+        <v>1.472028</v>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>0.289906</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Gain (loss) on change in fair value of derivative liabilities 52,257</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" s="5" t="n">
+        <v>-0.451372</v>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>0.022189</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Gain on termination of sales-type lease -</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" s="5" t="n">
+        <v>0.503544</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Accretion expense (509,871)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Loss on disposal of assets (155,692)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" s="5" t="n">
+        <v>-0.011655</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Impairment loss -</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" s="5" t="n">
+        <v>-1.202227</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Interest expense (293,675)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" s="5" t="n">
+        <v>-0.03521</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Other income 20,246</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="n">
+        <v>-0.016451</v>
+      </c>
+      <c r="F261" s="5" t="n">
+        <v>0.009209</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Net income from continuing operations before income tax expense 394,921</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="n">
+        <v>0.258657</v>
+      </c>
+      <c r="F262" s="5" t="n">
+        <v>0.321304</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Income tax expense (4,151,650)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" s="5" t="n">
+        <v>-3.482125</v>
+      </c>
+      <c r="F263" s="5" t="n">
+        <v>-0.372743</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Net loss from continuing operations after income tax expense (3,756,729)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" s="5" t="n">
+        <v>-3.223468</v>
+      </c>
+      <c r="F264" s="5" t="n">
+        <v>-0.051439</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Net loss from discontinued operations after income tax expense (212,813)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" s="5" t="n">
+        <v>-0.081817</v>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>-0.022965</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>ended</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Net loss (3,969,542)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" s="5" t="n">
+        <v>-3.305285</v>
+      </c>
+      <c r="F266" s="5" t="n">
+        <v>-0.074404</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment 133,050</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" s="5" t="n">
+        <v>0.015089</v>
+      </c>
+      <c r="F267" s="5" t="n">
+        <v>0.000808</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Comprehensive loss (3,836,492)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" s="5" t="n">
+        <v>-3.290196</v>
+      </c>
+      <c r="F268" s="5" t="n">
+        <v>-0.07359599999999999</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share from continuing operations (0.03)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="F269" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share from discontinued operations (0.00)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (0.03)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="F271" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - basic 119,794,951</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="n">
+        <v>120.047814</v>
+      </c>
+      <c r="F272" s="5" t="n">
+        <v>120.047814</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - diluted 120,588,044</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="n">
+        <v>122.880907</v>
+      </c>
+      <c r="F273" s="5" t="n">
+        <v>122.880907</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2023 120,047,814 105,445,792 628,141 (2,287,145)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" s="5" t="n">
+        <v>34.315076</v>
+      </c>
+      <c r="F274" s="5" t="n">
+        <v>-69.471712</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Share-based compensation - 22,128 - -</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" s="5" t="n">
+        <v>0.022128</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive income for the year - - - 15,089</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" s="5" t="n">
+        <v>-3.290196</v>
+      </c>
+      <c r="F276" s="5" t="n">
+        <v>-3.305285</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2024 120,047,814 105,467,920 628,141 (2,272,056)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" s="5" t="n">
+        <v>31.047008</v>
+      </c>
+      <c r="F277" s="5" t="n">
+        <v>-72.77699699999999</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive income for the year - - - 808</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" s="5" t="n">
+        <v>-0.07359599999999999</v>
+      </c>
+      <c r="F278" s="5" t="n">
+        <v>-0.074404</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2024 120,047,814 105,467,920 628,141 (2,271,248)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" s="5" t="n">
+        <v>30.973412</v>
+      </c>
+      <c r="F279" s="5" t="n">
+        <v>-72.851401</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Warrants issued in private placement - 966,028 - -</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" s="5" t="n">
+        <v>0.966028</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Share-based compensation - 849,559 - -</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" s="5" t="n">
+        <v>0.849559</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Cancellation of shares (2,051,000) (276,730) - -</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" s="5" t="n">
+        <v>-0.27673</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive income for the year - - - 133,050</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" s="5" t="n">
+        <v>-3.836492</v>
+      </c>
+      <c r="F283" s="5" t="n">
+        <v>-3.969542</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2025 117,996,814 107,006,777 628,141 (2,138,198)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" s="5" t="n">
+        <v>28.675777</v>
+      </c>
+      <c r="F284" s="5" t="n">
+        <v>-76.820943</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>March 31, January</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Revenue 4,464,950</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="n">
+        <v>28.2852</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Cost of sales 2,688,650</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="n">
+        <v>17.135434</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Gross profit 1,776,300</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="n">
+        <v>11.149766</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Selling, general and administrative expenses 1,486,394</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="n">
+        <v>9.677738</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Income from operations 289,906</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="n">
+        <v>1.472028</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Gain (loss) on change in fair value of derivative liability 22,189</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" s="5" t="n">
+        <v>-0.451372</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Gain on termination of sales-type lease and disposal of licenses -</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" s="5" t="n">
+        <v>0.503544</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Loss on disposal of assets -</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" s="5" t="n">
+        <v>-0.011655</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Impairment loss -</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" s="5" t="n">
+        <v>-1.202227</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Interest expense -</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="n">
+        <v>-0.03521</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Other expense 9,209</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="n">
+        <v>-0.016451</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Net income from continuing operations before income tax expense 321,304</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="n">
+        <v>0.258657</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Income tax expense (372,743)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" s="5" t="n">
+        <v>-3.482125</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Net loss from continuing operations after income tax expense (51,439)</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" s="5" t="n">
+        <v>-3.223468</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Net loss from discontinued operations after income tax expense (22,965)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" s="5" t="n">
+        <v>-0.081817</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Net loss (74,404)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" s="5" t="n">
+        <v>-3.305285</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment 808</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" s="5" t="n">
+        <v>0.015089</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Comprehensive loss (73,596)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" s="5" t="n">
+        <v>-3.290196</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share from continuing operations (0.00)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (0.00)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - basic and diluted 120,047,814</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" s="5" t="n">
+        <v>120.047814</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2023 120,047,814 105,445,792 628,141 (2,287,145) (69,471,712)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" s="5" t="n">
+        <v>34.315076</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Share-based compensation - 22,128 - - -</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" s="5" t="n">
+        <v>0.022128</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Net loss and other comprehensive income for the year - - - 15,089 (3,305,285)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" s="5" t="n">
+        <v>-3.290196</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Balance, January 31, 2024 120,047,814 105,467,920 628,141 (2,272,056) (72,776,997)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" s="5" t="n">
+        <v>31.047008</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Net loss and other comprehensive income for the year - - - 808 (74,404)</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" s="5" t="n">
+        <v>-0.07359599999999999</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
         <is>
           <t>Balance, March 31, 2024 120,047,814 105,467,920 628,141 (2,271,248) (72,851,401)</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" s="5" t="n">
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" s="5" t="n">
         <v>30.973412</v>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
         <is>
           <t>-</t>
         </is>
